--- a/data/trans_camb/IP1004-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1004-Habitat-trans_camb.xlsx
@@ -631,12 +631,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,0</t>
+          <t>-2,63; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,42</t>
+          <t>-1,05; 2,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,0</t>
+          <t>-1,26; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,33</t>
+          <t>-0,5; 1,21</t>
         </is>
       </c>
     </row>
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,03; -0,31</t>
+          <t>-2,84; -0,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,16; -0,32</t>
+          <t>-2,79; -0,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; -0,16</t>
+          <t>-1,64; -0,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; -0,16</t>
+          <t>-1,62; -0,16</t>
         </is>
       </c>
     </row>
@@ -953,12 +953,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,63</t>
+          <t>-0,91; 1,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 0,0</t>
+          <t>-2,69; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,0</t>
+          <t>-1,17; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,17 +1099,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,15</t>
+          <t>-0,66; 1,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,0</t>
+          <t>-1,97; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 1,31</t>
+          <t>-0,16; 1,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,0</t>
+          <t>-0,82; 0,0</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,33</t>
+          <t>-0,51; 0,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,38</t>
+          <t>-0,42; 0,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,36</t>
+          <t>-0,62; 0,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; -0,17</t>
+          <t>-1,02; -0,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,24</t>
+          <t>-0,46; 0,19</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,0</t>
+          <t>-0,61; -0,0</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 368,78</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-87,83; 178,42</t>
+          <t>-87,33; 175,47</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 68,45</t>
+          <t>-100,0; 73,73</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1004-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1004-Habitat-trans_camb.xlsx
@@ -631,12 +631,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,0</t>
+          <t>-2,66; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,4</t>
+          <t>-1,05; 2,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,21</t>
+          <t>-0,5; 1,2</t>
         </is>
       </c>
     </row>
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,84; -0,28</t>
+          <t>-2,81; -0,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,79; -0,31</t>
+          <t>-3,17; -0,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; -0,16</t>
+          <t>-1,46; -0,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; -0,16</t>
+          <t>-1,47; -0,16</t>
         </is>
       </c>
     </row>
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,6</t>
+          <t>-0,9; 1,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 0,0</t>
+          <t>-2,25; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,81</t>
+          <t>-0,47; 0,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,0</t>
+          <t>-1,25; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,18</t>
+          <t>-0,66; 1,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 0,0</t>
+          <t>-2,21; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 1,27</t>
+          <t>-0,16; 1,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,0</t>
+          <t>-0,84; 0,0</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,23</t>
+          <t>-0,52; 0,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,39</t>
+          <t>-0,42; 0,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,46</t>
+          <t>-0,64; 0,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,02; -0,17</t>
+          <t>-1,0; -0,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,19</t>
+          <t>-0,42; 0,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,61; -0,0</t>
+          <t>-0,57; -0,0</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 368,78</t>
+          <t>-100,0; 352,0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-87,33; 175,47</t>
+          <t>-85,69; 230,9</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 73,73</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1004-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1004-Habitat-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-0,53</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,49</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,65; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,05; 2,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,0</t>
+          <t>-1,25; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,2</t>
+          <t>-0,5; 1,33</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>92,85%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,22</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,22</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,22</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,22</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,03; -0,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,16; -0,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,81; -0,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,17; -0,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,46; -0,15</t>
+          <t>-1,47; -0,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; -0,16</t>
+          <t>-1,55; -0,16</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,07</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,45</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,91; 1,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,6; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,84</t>
+          <t>-0,47; 0,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,0</t>
+          <t>-1,35; 0,0</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>14,87%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>14,87%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,73</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,05</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-0,33</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,73</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,27</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>-0,93; 1,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,64; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 1,45</t>
+          <t>-0,15; 1,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 0,0</t>
+          <t>-1,11; 0,0</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>15,11%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,13</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,45</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-0,1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-0,01</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,23</t>
+          <t>-0,67; 0,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,37</t>
+          <t>-1,0; -0,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,41</t>
+          <t>-0,42; 0,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; -0,17</t>
+          <t>-0,42; 0,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,24</t>
+          <t>-0,43; 0,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; -0,0</t>
+          <t>-0,54; 0,0</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-29,4%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-46,2%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-7,07%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-29,4%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 352,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-85,69; 230,9</t>
+          <t>-87,83; 178,42</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 68,45</t>
         </is>
       </c>
     </row>
